--- a/Statistic.xlsx
+++ b/Statistic.xlsx
@@ -4,21 +4,163 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="120" yWindow="105" windowWidth="15120" windowHeight="8010"/>
+    <workbookView xWindow="120" yWindow="105" windowWidth="15120" windowHeight="8010" activeTab="3"/>
   </bookViews>
   <sheets>
-    <sheet name="Лист1" sheetId="1" r:id="rId1"/>
-    <sheet name="Лист2" sheetId="2" r:id="rId2"/>
-    <sheet name="Лист3" sheetId="3" r:id="rId3"/>
+    <sheet name="1" sheetId="1" r:id="rId1"/>
+    <sheet name="2" sheetId="4" r:id="rId2"/>
+    <sheet name="Перш" sheetId="2" r:id="rId3"/>
+    <sheet name="Звед 2" sheetId="5" r:id="rId4"/>
+    <sheet name="Лист3" sheetId="3" r:id="rId5"/>
   </sheets>
-  <calcPr calcId="122211"/>
+  <calcPr calcId="124519"/>
+  <pivotCaches>
+    <pivotCache cacheId="101" r:id="rId6"/>
+  </pivotCaches>
 </workbook>
+</file>
+
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="41">
+  <si>
+    <t>Вид робіт</t>
+  </si>
+  <si>
+    <t>План</t>
+  </si>
+  <si>
+    <t>Створення акаунта</t>
+  </si>
+  <si>
+    <t>Вхід у CRM</t>
+  </si>
+  <si>
+    <t>Налаштування CRM для послуг</t>
+  </si>
+  <si>
+    <t>Налаштування CRM для онлайн торгівлі</t>
+  </si>
+  <si>
+    <t>Факт</t>
+  </si>
+  <si>
+    <t>Підсумок</t>
+  </si>
+  <si>
+    <t>Етап 5</t>
+  </si>
+  <si>
+    <t>Етап 6</t>
+  </si>
+  <si>
+    <t>Етап 7</t>
+  </si>
+  <si>
+    <t>Етап 8</t>
+  </si>
+  <si>
+    <t>Етап 9</t>
+  </si>
+  <si>
+    <t>Етап 10</t>
+  </si>
+  <si>
+    <t>Етап 11</t>
+  </si>
+  <si>
+    <t>Етап 12</t>
+  </si>
+  <si>
+    <t>Етап 13</t>
+  </si>
+  <si>
+    <t>Етап 14</t>
+  </si>
+  <si>
+    <t>Етап 15</t>
+  </si>
+  <si>
+    <t>Етап 16</t>
+  </si>
+  <si>
+    <t>Етап 17</t>
+  </si>
+  <si>
+    <t>Етап 18</t>
+  </si>
+  <si>
+    <t>Етап 19</t>
+  </si>
+  <si>
+    <t>Етап 20</t>
+  </si>
+  <si>
+    <t>Етап 21</t>
+  </si>
+  <si>
+    <t>Етап 22</t>
+  </si>
+  <si>
+    <t>Етап 23</t>
+  </si>
+  <si>
+    <t>Етап 24</t>
+  </si>
+  <si>
+    <t>Етап 25</t>
+  </si>
+  <si>
+    <t>Етап 26</t>
+  </si>
+  <si>
+    <t>Дата</t>
+  </si>
+  <si>
+    <t>Відсоток  виконання</t>
+  </si>
+  <si>
+    <t>Названия строк</t>
+  </si>
+  <si>
+    <t>Общий итог</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Відсоток  виконання</t>
+  </si>
+  <si>
+    <t>Названия столбцов</t>
+  </si>
+  <si>
+    <t>Настройки- комунікації</t>
+  </si>
+  <si>
+    <t>Налаштування - джерела</t>
+  </si>
+  <si>
+    <t>завантаження данних за останні два місяці</t>
+  </si>
+  <si>
+    <t>Канали комунікацій</t>
+  </si>
+  <si>
+    <t>Джерела данних</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="1">
+  <fonts count="2">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -35,7 +177,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -43,12 +185,36 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -56,6 +222,1263 @@
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <c:lang val="ru-RU"/>
+  <c:chart>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="bar"/>
+        <c:grouping val="clustered"/>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:v>Виконано</c:v>
+          </c:tx>
+          <c:cat>
+            <c:strRef>
+              <c:f>'1'!$B$3:$B$28</c:f>
+              <c:strCache>
+                <c:ptCount val="26"/>
+                <c:pt idx="0">
+                  <c:v>Створення акаунта</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Вхід у CRM</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Налаштування CRM для послуг</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Налаштування CRM для онлайн торгівлі</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Етап 5</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Етап 6</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>Етап 7</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>Етап 8</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>Етап 9</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>Етап 10</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>Етап 11</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>Етап 12</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>Етап 13</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>Етап 14</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>Етап 15</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>Етап 16</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>Етап 17</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>Етап 18</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>Етап 19</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>Етап 20</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>Етап 21</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>Етап 22</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>Етап 23</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>Етап 24</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>Етап 25</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>Етап 26</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'1'!$D$3:$D$28</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="26"/>
+                <c:pt idx="0">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:v>Заплановано</c:v>
+          </c:tx>
+          <c:cat>
+            <c:strRef>
+              <c:f>'1'!$B$3:$B$28</c:f>
+              <c:strCache>
+                <c:ptCount val="26"/>
+                <c:pt idx="0">
+                  <c:v>Створення акаунта</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Вхід у CRM</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Налаштування CRM для послуг</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Налаштування CRM для онлайн торгівлі</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Етап 5</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Етап 6</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>Етап 7</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>Етап 8</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>Етап 9</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>Етап 10</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>Етап 11</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>Етап 12</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>Етап 13</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>Етап 14</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>Етап 15</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>Етап 16</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>Етап 17</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>Етап 18</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>Етап 19</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>Етап 20</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>Етап 21</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>Етап 22</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>Етап 23</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>Етап 24</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>Етап 25</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>Етап 26</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'1'!$C$3:$C$28</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="26"/>
+                <c:pt idx="0">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>10</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:axId val="81170432"/>
+        <c:axId val="81172736"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="81170432"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:axPos val="l"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="81172736"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="81172736"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:axPos val="b"/>
+        <c:majorGridlines/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="81170432"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:layout/>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+  </c:chart>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <c:lang val="ru-RU"/>
+  <c:chart>
+    <c:title>
+      <c:layout/>
+    </c:title>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="bar"/>
+        <c:grouping val="clustered"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'2'!$C$2</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Відсоток  виконання</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:cat>
+            <c:strRef>
+              <c:f>'2'!$B$3:$B$28</c:f>
+              <c:strCache>
+                <c:ptCount val="26"/>
+                <c:pt idx="0">
+                  <c:v>Етап 10</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Етап 11</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Етап 12</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Етап 13</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Етап 14</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Етап 15</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>Етап 16</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>Етап 17</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>Етап 18</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>Етап 19</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>Етап 20</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>Етап 21</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>Етап 22</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>Етап 23</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>Етап 24</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>Етап 25</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>Етап 26</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>Етап 5</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>Етап 6</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>Етап 7</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>Етап 8</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>Етап 9</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>Налаштування CRM для онлайн торгівлі</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>Налаштування CRM для послуг</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>Вхід у CRM</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>Створення акаунта</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'2'!$C$3:$C$28</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="26"/>
+                <c:pt idx="23">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>100</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>100</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:axId val="39136640"/>
+        <c:axId val="39171200"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="39136640"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:axPos val="l"/>
+        <c:numFmt formatCode="dd/mm/yyyy" sourceLinked="1"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="39171200"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="39171200"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:axPos val="b"/>
+        <c:majorGridlines/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="39136640"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:layout/>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+  </c:chart>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <c:lang val="ru-RU"/>
+  <c:pivotSource>
+    <c:name>[Statistic.xlsx]Звед 2!СводнаяТаблица1</c:name>
+    <c:fmtId val="0"/>
+  </c:pivotSource>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="ru-RU"/>
+              <a:t>Успіхи в начанні </a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>key-CRM</a:t>
+            </a:r>
+            <a:endParaRPr lang="ru-RU"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:layout>
+        <c:manualLayout>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="3.0771353580802401E-2"/>
+          <c:y val="1.777778364706702E-2"/>
+        </c:manualLayout>
+      </c:layout>
+    </c:title>
+    <c:pivotFmts>
+      <c:pivotFmt>
+        <c:idx val="0"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="bg1">
+              <a:lumMod val="95000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </c:spPr>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="1"/>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="2"/>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:layout/>
+          <c:spPr/>
+          <c:txPr>
+            <a:bodyPr/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr/>
+              </a:pPr>
+              <a:endParaRPr lang="ru-RU"/>
+            </a:p>
+          </c:txPr>
+          <c:showSerName val="1"/>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="3"/>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="4"/>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:layout/>
+          <c:spPr/>
+          <c:txPr>
+            <a:bodyPr/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr/>
+              </a:pPr>
+              <a:endParaRPr lang="ru-RU"/>
+            </a:p>
+          </c:txPr>
+          <c:showSerName val="1"/>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="5"/>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:layout/>
+          <c:spPr/>
+          <c:txPr>
+            <a:bodyPr/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr/>
+              </a:pPr>
+              <a:endParaRPr lang="ru-RU"/>
+            </a:p>
+          </c:txPr>
+          <c:showSerName val="1"/>
+        </c:dLbl>
+      </c:pivotFmt>
+    </c:pivotFmts>
+    <c:plotArea>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.28258419582060579"/>
+          <c:y val="0.19924163325738128"/>
+          <c:w val="0.59258936169162169"/>
+          <c:h val="0.63862940209396912"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:barChart>
+        <c:barDir val="bar"/>
+        <c:grouping val="clustered"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Звед 2'!$B$3:$B$4</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>03.06.2026</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:dLbls>
+            <c:spPr/>
+            <c:txPr>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:endParaRPr lang="ru-RU"/>
+              </a:p>
+            </c:txPr>
+            <c:showSerName val="1"/>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Звед 2'!$A$5:$A$9</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>Джерела данних</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Канали комунікацій</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Створення акаунта</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Вхід у CRM</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Звед 2'!$B$5:$B$9</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>80</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>80</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>100</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>100</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:axId val="105140224"/>
+        <c:axId val="105472768"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="105140224"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:axPos val="l"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="105472768"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="105472768"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:max val="100"/>
+        </c:scaling>
+        <c:axPos val="b"/>
+        <c:majorGridlines/>
+        <c:numFmt formatCode="General" sourceLinked="0"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="105140224"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:solidFill>
+          <a:schemeClr val="bg1">
+            <a:lumMod val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1">
+        <a:lumMod val="50000"/>
+      </a:schemeClr>
+    </a:solidFill>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr>
+          <a:solidFill>
+            <a:schemeClr val="bg1"/>
+          </a:solidFill>
+        </a:defRPr>
+      </a:pPr>
+      <a:endParaRPr lang="ru-RU"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>19048</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>9524</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>457200</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Диаграмма 2"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>609599</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>9524</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>47625</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>66675</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="10" name="Диаграмма 9"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>19050</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>19051</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>561975</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>66675</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Диаграмма 1"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1" refreshedBy="Автор" refreshedDate="46176.89473738426" createdVersion="3" refreshedVersion="3" minRefreshableVersion="3" recordCount="29">
+  <cacheSource type="worksheet">
+    <worksheetSource ref="B2:D31" sheet="Перш"/>
+  </cacheSource>
+  <cacheFields count="3">
+    <cacheField name="Вид робіт" numFmtId="0">
+      <sharedItems containsBlank="1" containsMixedTypes="1" containsNumber="1" containsInteger="1" minValue="5" maxValue="26" count="29">
+        <s v="Створення акаунта"/>
+        <s v="Вхід у CRM"/>
+        <s v="Канали комунікацій"/>
+        <s v="Джерела данних"/>
+        <s v="Налаштування CRM для послуг"/>
+        <s v="Налаштування CRM для онлайн торгівлі"/>
+        <m/>
+        <n v="5"/>
+        <n v="6"/>
+        <n v="7"/>
+        <n v="8"/>
+        <n v="9"/>
+        <n v="10"/>
+        <n v="11"/>
+        <n v="12"/>
+        <n v="13"/>
+        <n v="14"/>
+        <n v="15"/>
+        <n v="16"/>
+        <n v="17"/>
+        <n v="18"/>
+        <n v="19"/>
+        <n v="20"/>
+        <n v="21"/>
+        <n v="22"/>
+        <n v="23"/>
+        <n v="24"/>
+        <n v="25"/>
+        <n v="26"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="Відсоток  виконання" numFmtId="0">
+      <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="80" maxValue="100"/>
+    </cacheField>
+    <cacheField name="Дата" numFmtId="0">
+      <sharedItems containsNonDate="0" containsDate="1" containsString="0" containsBlank="1" minDate="2026-06-03T00:00:00" maxDate="2026-06-06T00:00:00" count="4">
+        <d v="2026-06-03T00:00:00"/>
+        <m/>
+        <d v="2026-06-05T00:00:00" u="1"/>
+        <d v="2026-06-04T00:00:00" u="1"/>
+      </sharedItems>
+    </cacheField>
+  </cacheFields>
+</pivotCacheDefinition>
+</file>
+
+<file path=xl/pivotCache/pivotCacheRecords1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" count="29">
+  <r>
+    <x v="0"/>
+    <n v="100"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <n v="100"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <n v="80"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <n v="80"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="4"/>
+    <m/>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="5"/>
+    <m/>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="6"/>
+    <m/>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="7"/>
+    <m/>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="8"/>
+    <m/>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="9"/>
+    <m/>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="10"/>
+    <m/>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="11"/>
+    <m/>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="12"/>
+    <m/>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="13"/>
+    <m/>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="14"/>
+    <m/>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="15"/>
+    <m/>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="16"/>
+    <m/>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="17"/>
+    <m/>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="18"/>
+    <m/>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="19"/>
+    <m/>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="20"/>
+    <m/>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="21"/>
+    <m/>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="22"/>
+    <m/>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="23"/>
+    <m/>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="24"/>
+    <m/>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="25"/>
+    <m/>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="26"/>
+    <m/>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="27"/>
+    <m/>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="28"/>
+    <m/>
+    <x v="1"/>
+  </r>
+</pivotCacheRecords>
+</file>
+
+<file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="СводнаяТаблица1" cacheId="101" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Значения" updatedVersion="3" minRefreshableVersion="3" showCalcMbrs="0" useAutoFormatting="1" itemPrintTitles="1" createdVersion="3" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1">
+  <location ref="A3:C9" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
+  <pivotFields count="3">
+    <pivotField axis="axisRow" showAll="0">
+      <items count="30">
+        <item x="28"/>
+        <item x="27"/>
+        <item x="26"/>
+        <item x="25"/>
+        <item x="24"/>
+        <item x="23"/>
+        <item x="22"/>
+        <item x="21"/>
+        <item x="20"/>
+        <item x="19"/>
+        <item x="18"/>
+        <item x="17"/>
+        <item x="16"/>
+        <item x="15"/>
+        <item x="14"/>
+        <item x="13"/>
+        <item x="12"/>
+        <item x="11"/>
+        <item x="10"/>
+        <item x="9"/>
+        <item x="8"/>
+        <item x="7"/>
+        <item x="5"/>
+        <item x="4"/>
+        <item x="6"/>
+        <item x="3"/>
+        <item x="2"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField axis="axisCol" showAll="0">
+      <items count="5">
+        <item m="1" x="2"/>
+        <item m="1" x="3"/>
+        <item h="1" x="1"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="0"/>
+  </rowFields>
+  <rowItems count="5">
+    <i>
+      <x v="25"/>
+    </i>
+    <i>
+      <x v="26"/>
+    </i>
+    <i>
+      <x v="27"/>
+    </i>
+    <i>
+      <x v="28"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="2"/>
+  </colFields>
+  <colItems count="2">
+    <i>
+      <x v="3"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="  Відсоток  виконання" fld="1" baseField="0" baseItem="0"/>
+  </dataFields>
+  <chartFormats count="5">
+    <chartFormat chart="0" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="2" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="3" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="4" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="3"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="5" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+</pivotTableDefinition>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -343,29 +1766,929 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1"/>
+  <dimension ref="A2:D30"/>
   <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData/>
+  <cols>
+    <col min="2" max="2" width="38" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:4">
+      <c r="B2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3" s="2">
+        <v>10</v>
+      </c>
+      <c r="D3" s="2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4">
+        <v>2</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C4" s="2">
+        <v>10</v>
+      </c>
+      <c r="D4" s="2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5">
+        <v>3</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C5" s="2">
+        <v>10</v>
+      </c>
+      <c r="D5" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6">
+        <v>4</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C6" s="2">
+        <v>10</v>
+      </c>
+      <c r="D6" s="2"/>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="B7" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C7" s="2">
+        <v>10</v>
+      </c>
+      <c r="D7" s="2"/>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="B8" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="2">
+        <v>10</v>
+      </c>
+      <c r="D8" s="2"/>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="B9" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C9" s="2">
+        <v>10</v>
+      </c>
+      <c r="D9" s="2"/>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="B10" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C10" s="2">
+        <v>10</v>
+      </c>
+      <c r="D10" s="2"/>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="B11" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C11" s="2">
+        <v>10</v>
+      </c>
+      <c r="D11" s="2"/>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="B12" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C12" s="2">
+        <v>10</v>
+      </c>
+      <c r="D12" s="2"/>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="B13" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C13" s="2">
+        <v>10</v>
+      </c>
+      <c r="D13" s="2"/>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="B14" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C14" s="2">
+        <v>10</v>
+      </c>
+      <c r="D14" s="2"/>
+    </row>
+    <row r="15" spans="1:4">
+      <c r="B15" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C15" s="2">
+        <v>10</v>
+      </c>
+      <c r="D15" s="2"/>
+    </row>
+    <row r="16" spans="1:4">
+      <c r="B16" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C16" s="2">
+        <v>10</v>
+      </c>
+      <c r="D16" s="2"/>
+    </row>
+    <row r="17" spans="2:4">
+      <c r="B17" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C17" s="2">
+        <v>10</v>
+      </c>
+      <c r="D17" s="2"/>
+    </row>
+    <row r="18" spans="2:4">
+      <c r="B18" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C18" s="2">
+        <v>10</v>
+      </c>
+      <c r="D18" s="2"/>
+    </row>
+    <row r="19" spans="2:4">
+      <c r="B19" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C19" s="2">
+        <v>10</v>
+      </c>
+      <c r="D19" s="2"/>
+    </row>
+    <row r="20" spans="2:4">
+      <c r="B20" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C20" s="2">
+        <v>10</v>
+      </c>
+      <c r="D20" s="2"/>
+    </row>
+    <row r="21" spans="2:4">
+      <c r="B21" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C21" s="2">
+        <v>10</v>
+      </c>
+      <c r="D21" s="2"/>
+    </row>
+    <row r="22" spans="2:4">
+      <c r="B22" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C22" s="2">
+        <v>10</v>
+      </c>
+      <c r="D22" s="2"/>
+    </row>
+    <row r="23" spans="2:4">
+      <c r="B23" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C23" s="2">
+        <v>10</v>
+      </c>
+      <c r="D23" s="2"/>
+    </row>
+    <row r="24" spans="2:4">
+      <c r="B24" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C24" s="2">
+        <v>10</v>
+      </c>
+      <c r="D24" s="2"/>
+    </row>
+    <row r="25" spans="2:4">
+      <c r="B25" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C25" s="2">
+        <v>10</v>
+      </c>
+      <c r="D25" s="2"/>
+    </row>
+    <row r="26" spans="2:4">
+      <c r="B26" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C26" s="2">
+        <v>10</v>
+      </c>
+      <c r="D26" s="2"/>
+    </row>
+    <row r="27" spans="2:4">
+      <c r="B27" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C27" s="2">
+        <v>10</v>
+      </c>
+      <c r="D27" s="2"/>
+    </row>
+    <row r="28" spans="2:4">
+      <c r="B28" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C28" s="2">
+        <v>10</v>
+      </c>
+      <c r="D28" s="2"/>
+    </row>
+    <row r="29" spans="2:4">
+      <c r="B29" s="2"/>
+      <c r="C29" s="2"/>
+      <c r="D29" s="2"/>
+    </row>
+    <row r="30" spans="2:4">
+      <c r="B30" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C30" s="2">
+        <f>SUM(C3:C29)</f>
+        <v>260</v>
+      </c>
+      <c r="D30" s="2">
+        <f>SUM(D3:D29)</f>
+        <v>21</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="180" verticalDpi="180" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A2:D30"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="37.85546875" customWidth="1"/>
+    <col min="3" max="3" width="20.42578125" customWidth="1"/>
+    <col min="4" max="4" width="10.140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:4">
+      <c r="B2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3" s="2"/>
+      <c r="D3" s="2"/>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4" s="2"/>
+      <c r="D4" s="2"/>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="B6" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="B7" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" s="2"/>
+      <c r="D7" s="2"/>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="B8" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C8" s="2"/>
+      <c r="D8" s="2"/>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="B9" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C9" s="2"/>
+      <c r="D9" s="2"/>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="B10" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C10" s="2"/>
+      <c r="D10" s="2"/>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="B11" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C11" s="2"/>
+      <c r="D11" s="2"/>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="B12" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C12" s="2"/>
+      <c r="D12" s="2"/>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="B13" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C13" s="2"/>
+      <c r="D13" s="2"/>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="B14" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C14" s="2"/>
+      <c r="D14" s="2"/>
+    </row>
+    <row r="15" spans="1:4">
+      <c r="B15" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C15" s="2"/>
+      <c r="D15" s="2"/>
+    </row>
+    <row r="16" spans="1:4">
+      <c r="B16" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C16" s="2"/>
+      <c r="D16" s="2"/>
+    </row>
+    <row r="17" spans="1:4">
+      <c r="B17" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C17" s="2"/>
+      <c r="D17" s="2"/>
+    </row>
+    <row r="18" spans="1:4">
+      <c r="B18" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C18" s="2"/>
+      <c r="D18" s="2"/>
+    </row>
+    <row r="19" spans="1:4">
+      <c r="B19" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C19" s="2"/>
+      <c r="D19" s="2"/>
+    </row>
+    <row r="20" spans="1:4">
+      <c r="B20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C20" s="2"/>
+      <c r="D20" s="2"/>
+    </row>
+    <row r="21" spans="1:4">
+      <c r="B21" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C21" s="2"/>
+      <c r="D21" s="2"/>
+    </row>
+    <row r="22" spans="1:4">
+      <c r="B22" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C22" s="2"/>
+      <c r="D22" s="2"/>
+    </row>
+    <row r="23" spans="1:4">
+      <c r="B23" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C23" s="2"/>
+      <c r="D23" s="2"/>
+    </row>
+    <row r="24" spans="1:4">
+      <c r="B24" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C24" s="2"/>
+      <c r="D24" s="2"/>
+    </row>
+    <row r="25" spans="1:4">
+      <c r="B25" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C25" s="2"/>
+      <c r="D25" s="2"/>
+    </row>
+    <row r="26" spans="1:4">
+      <c r="B26" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C26" s="2">
+        <v>10</v>
+      </c>
+      <c r="D26" s="4">
+        <v>46177</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4">
+      <c r="A27">
+        <v>1</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C27" s="2">
+        <v>100</v>
+      </c>
+      <c r="D27" s="4">
+        <v>46176</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4">
+      <c r="B28" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C28" s="2">
+        <v>100</v>
+      </c>
+      <c r="D28" s="4">
+        <v>46176</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4">
+      <c r="B29" s="2"/>
+      <c r="C29" s="2"/>
+      <c r="D29" s="2"/>
+    </row>
+    <row r="30" spans="1:4">
+      <c r="B30" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C30" s="2">
+        <f>SUM(C3:C29)</f>
+        <v>210</v>
+      </c>
+      <c r="D30" s="2"/>
+    </row>
+  </sheetData>
+  <sortState ref="B3:D28">
+    <sortCondition ref="B3:B28"/>
+  </sortState>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="180" verticalDpi="180" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="B2:D33"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="38" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:4">
+      <c r="B2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="3" spans="2:4">
+      <c r="B3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3" s="2">
+        <v>100</v>
+      </c>
+      <c r="D3" s="4">
+        <v>46176</v>
+      </c>
+    </row>
+    <row r="4" spans="2:4">
+      <c r="B4" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C4" s="2">
+        <v>100</v>
+      </c>
+      <c r="D4" s="4">
+        <v>46176</v>
+      </c>
+    </row>
+    <row r="5" spans="2:4">
+      <c r="B5" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C5" s="2">
+        <v>80</v>
+      </c>
+      <c r="D5" s="4">
+        <v>46176</v>
+      </c>
+    </row>
+    <row r="6" spans="2:4">
+      <c r="B6" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C6" s="2">
+        <v>80</v>
+      </c>
+      <c r="D6" s="4">
+        <v>46176</v>
+      </c>
+    </row>
+    <row r="7" spans="2:4">
+      <c r="B7" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C7" s="2"/>
+      <c r="D7" s="4"/>
+    </row>
+    <row r="8" spans="2:4">
+      <c r="B8" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C8" s="2"/>
+      <c r="D8" s="4"/>
+    </row>
+    <row r="9" spans="2:4">
+      <c r="B9" s="2"/>
+      <c r="C9" s="2"/>
+      <c r="D9" s="4"/>
+    </row>
+    <row r="10" spans="2:4">
+      <c r="B10" s="2">
+        <v>5</v>
+      </c>
+      <c r="C10" s="2"/>
+      <c r="D10" s="2"/>
+    </row>
+    <row r="11" spans="2:4">
+      <c r="B11" s="2">
+        <v>6</v>
+      </c>
+      <c r="C11" s="2"/>
+      <c r="D11" s="2"/>
+    </row>
+    <row r="12" spans="2:4">
+      <c r="B12" s="2">
+        <v>7</v>
+      </c>
+      <c r="C12" s="2"/>
+      <c r="D12" s="2"/>
+    </row>
+    <row r="13" spans="2:4">
+      <c r="B13" s="2">
+        <v>8</v>
+      </c>
+      <c r="C13" s="2"/>
+      <c r="D13" s="2"/>
+    </row>
+    <row r="14" spans="2:4">
+      <c r="B14" s="2">
+        <v>9</v>
+      </c>
+      <c r="C14" s="2"/>
+      <c r="D14" s="2"/>
+    </row>
+    <row r="15" spans="2:4">
+      <c r="B15" s="2">
+        <v>10</v>
+      </c>
+      <c r="C15" s="2"/>
+      <c r="D15" s="2"/>
+    </row>
+    <row r="16" spans="2:4">
+      <c r="B16" s="2">
+        <v>11</v>
+      </c>
+      <c r="C16" s="2"/>
+      <c r="D16" s="2"/>
+    </row>
+    <row r="17" spans="2:4">
+      <c r="B17" s="2">
+        <v>12</v>
+      </c>
+      <c r="C17" s="2"/>
+      <c r="D17" s="2"/>
+    </row>
+    <row r="18" spans="2:4">
+      <c r="B18" s="2">
+        <v>13</v>
+      </c>
+      <c r="C18" s="2"/>
+      <c r="D18" s="2"/>
+    </row>
+    <row r="19" spans="2:4">
+      <c r="B19" s="2">
+        <v>14</v>
+      </c>
+      <c r="C19" s="2"/>
+      <c r="D19" s="2"/>
+    </row>
+    <row r="20" spans="2:4">
+      <c r="B20" s="2">
+        <v>15</v>
+      </c>
+      <c r="C20" s="2"/>
+      <c r="D20" s="2"/>
+    </row>
+    <row r="21" spans="2:4">
+      <c r="B21" s="2">
+        <v>16</v>
+      </c>
+      <c r="C21" s="2"/>
+      <c r="D21" s="2"/>
+    </row>
+    <row r="22" spans="2:4">
+      <c r="B22" s="2">
+        <v>17</v>
+      </c>
+      <c r="C22" s="2"/>
+      <c r="D22" s="2"/>
+    </row>
+    <row r="23" spans="2:4">
+      <c r="B23" s="2">
+        <v>18</v>
+      </c>
+      <c r="C23" s="2"/>
+      <c r="D23" s="2"/>
+    </row>
+    <row r="24" spans="2:4">
+      <c r="B24" s="2">
+        <v>19</v>
+      </c>
+      <c r="C24" s="2"/>
+      <c r="D24" s="2"/>
+    </row>
+    <row r="25" spans="2:4">
+      <c r="B25" s="2">
+        <v>20</v>
+      </c>
+      <c r="C25" s="2"/>
+      <c r="D25" s="2"/>
+    </row>
+    <row r="26" spans="2:4">
+      <c r="B26" s="2">
+        <v>21</v>
+      </c>
+      <c r="C26" s="2"/>
+      <c r="D26" s="2"/>
+    </row>
+    <row r="27" spans="2:4">
+      <c r="B27" s="2">
+        <v>22</v>
+      </c>
+      <c r="C27" s="2"/>
+      <c r="D27" s="2"/>
+    </row>
+    <row r="28" spans="2:4">
+      <c r="B28" s="2">
+        <v>23</v>
+      </c>
+      <c r="C28" s="2"/>
+      <c r="D28" s="2"/>
+    </row>
+    <row r="29" spans="2:4">
+      <c r="B29" s="2">
+        <v>24</v>
+      </c>
+      <c r="C29" s="2"/>
+      <c r="D29" s="2"/>
+    </row>
+    <row r="30" spans="2:4">
+      <c r="B30" s="2">
+        <v>25</v>
+      </c>
+      <c r="C30" s="2"/>
+      <c r="D30" s="2"/>
+    </row>
+    <row r="31" spans="2:4">
+      <c r="B31" s="2">
+        <v>26</v>
+      </c>
+      <c r="C31" s="2"/>
+      <c r="D31" s="2"/>
+    </row>
+    <row r="32" spans="2:4">
+      <c r="B32" s="2"/>
+      <c r="C32" s="2"/>
+      <c r="D32" s="2"/>
+    </row>
+    <row r="33" spans="2:4">
+      <c r="B33" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C33" s="2">
+        <f>SUM(C3:C32)</f>
+        <v>360</v>
+      </c>
+      <c r="D33" s="2"/>
+    </row>
+  </sheetData>
+  <sortState ref="B3:D28">
+    <sortCondition descending="1" ref="B3:B28"/>
+  </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="180" verticalDpi="180" r:id="rId1"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1"/>
+  <dimension ref="A3:C9"/>
   <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="20.7109375" customWidth="1"/>
+    <col min="2" max="2" width="20.85546875" customWidth="1"/>
+    <col min="3" max="3" width="11.85546875" customWidth="1"/>
+    <col min="4" max="4" width="10.140625" customWidth="1"/>
+    <col min="5" max="6" width="11.85546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="1:3">
+      <c r="A3" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="B4" s="3">
+        <v>46176</v>
+      </c>
+      <c r="C4" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B5" s="7">
+        <v>80</v>
+      </c>
+      <c r="C5" s="7">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B6" s="7">
+        <v>80</v>
+      </c>
+      <c r="C6" s="7">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="B7" s="7">
+        <v>100</v>
+      </c>
+      <c r="C7" s="7">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="B8" s="7">
+        <v>100</v>
+      </c>
+      <c r="C8" s="7">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="B9" s="7">
+        <v>360</v>
+      </c>
+      <c r="C9" s="7">
+        <v>360</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="180" verticalDpi="180" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1"/>
+  <dimension ref="B3:D4"/>
   <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData/>
+  <cols>
+    <col min="2" max="2" width="24.28515625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="2:4">
+      <c r="B3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="4" spans="2:4">
+      <c r="B4" t="s">
+        <v>37</v>
+      </c>
+      <c r="D4" t="s">
+        <v>38</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="180" verticalDpi="180" r:id="rId1"/>
 </worksheet>

--- a/Statistic.xlsx
+++ b/Statistic.xlsx
@@ -15,13 +15,13 @@
   </sheets>
   <calcPr calcId="124519"/>
   <pivotCaches>
-    <pivotCache cacheId="101" r:id="rId6"/>
+    <pivotCache cacheId="42" r:id="rId6"/>
   </pivotCaches>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="41">
   <si>
     <t>Вид робіт</t>
   </si>
@@ -204,7 +204,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -215,6 +215,9 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -524,24 +527,24 @@
             </c:numRef>
           </c:val>
         </c:ser>
-        <c:axId val="81170432"/>
-        <c:axId val="81172736"/>
+        <c:axId val="117803264"/>
+        <c:axId val="117821440"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="81170432"/>
+        <c:axId val="117803264"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
         <c:axPos val="l"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="81172736"/>
+        <c:crossAx val="117821440"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
         <c:lblOffset val="100"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="81172736"/>
+        <c:axId val="117821440"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -549,20 +552,19 @@
         <c:majorGridlines/>
         <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="81170432"/>
+        <c:crossAx val="117803264"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
     </c:plotArea>
     <c:legend>
       <c:legendPos val="r"/>
-      <c:layout/>
     </c:legend>
     <c:plotVisOnly val="1"/>
   </c:chart>
   <c:printSettings>
     <c:headerFooter/>
-    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageMargins b="0.75000000000000011" l="0.70000000000000007" r="0.70000000000000007" t="0.75000000000000011" header="0.30000000000000004" footer="0.30000000000000004"/>
     <c:pageSetup/>
   </c:printSettings>
 </c:chartSpace>
@@ -572,9 +574,7 @@
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <c:lang val="ru-RU"/>
   <c:chart>
-    <c:title>
-      <c:layout/>
-    </c:title>
+    <c:title/>
     <c:plotArea>
       <c:layout/>
       <c:barChart>
@@ -699,25 +699,25 @@
             </c:numRef>
           </c:val>
         </c:ser>
-        <c:axId val="39136640"/>
-        <c:axId val="39171200"/>
+        <c:axId val="118033792"/>
+        <c:axId val="118051968"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="39136640"/>
+        <c:axId val="118033792"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
         <c:axPos val="l"/>
         <c:numFmt formatCode="dd/mm/yyyy" sourceLinked="1"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="39171200"/>
+        <c:crossAx val="118051968"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
         <c:lblOffset val="100"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="39171200"/>
+        <c:axId val="118051968"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -725,20 +725,19 @@
         <c:majorGridlines/>
         <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="39136640"/>
+        <c:crossAx val="118033792"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
     </c:plotArea>
     <c:legend>
       <c:legendPos val="r"/>
-      <c:layout/>
     </c:legend>
     <c:plotVisOnly val="1"/>
   </c:chart>
   <c:printSettings>
     <c:headerFooter/>
-    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageMargins b="0.75000000000000011" l="0.70000000000000007" r="0.70000000000000007" t="0.75000000000000011" header="0.30000000000000004" footer="0.30000000000000004"/>
     <c:pageSetup/>
   </c:printSettings>
 </c:chartSpace>
@@ -777,8 +776,8 @@
         <c:manualLayout>
           <c:xMode val="edge"/>
           <c:yMode val="edge"/>
-          <c:x val="3.0771353580802401E-2"/>
-          <c:y val="1.777778364706702E-2"/>
+          <c:x val="3.0771353580802407E-2"/>
+          <c:y val="1.7777783647067023E-2"/>
         </c:manualLayout>
       </c:layout>
     </c:title>
@@ -856,7 +855,6 @@
         </c:marker>
         <c:dLbl>
           <c:idx val="0"/>
-          <c:layout/>
           <c:spPr/>
           <c:txPr>
             <a:bodyPr/>
@@ -878,10 +876,10 @@
           <c:layoutTarget val="inner"/>
           <c:xMode val="edge"/>
           <c:yMode val="edge"/>
-          <c:x val="0.28258419582060579"/>
-          <c:y val="0.19924163325738128"/>
-          <c:w val="0.59258936169162169"/>
-          <c:h val="0.63862940209396912"/>
+          <c:x val="0.28258419582060595"/>
+          <c:y val="0.19924163325738131"/>
+          <c:w val="0.59258936169162146"/>
+          <c:h val="0.63862940209396934"/>
         </c:manualLayout>
       </c:layout>
       <c:barChart>
@@ -896,7 +894,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>03.06.2026</c:v>
+                  <c:v>04.06.2026</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -917,19 +915,22 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'Звед 2'!$A$5:$A$9</c:f>
+              <c:f>'Звед 2'!$A$5:$A$10</c:f>
               <c:strCache>
-                <c:ptCount val="4"/>
+                <c:ptCount val="5"/>
                 <c:pt idx="0">
+                  <c:v>Налаштування CRM для послуг</c:v>
+                </c:pt>
+                <c:pt idx="1">
                   <c:v>Джерела данних</c:v>
                 </c:pt>
-                <c:pt idx="1">
+                <c:pt idx="2">
                   <c:v>Канали комунікацій</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="3">
                   <c:v>Створення акаунта</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="4">
                   <c:v>Вхід у CRM</c:v>
                 </c:pt>
               </c:strCache>
@@ -937,44 +938,108 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Звед 2'!$B$5:$B$9</c:f>
+              <c:f>'Звед 2'!$B$5:$B$10</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="4"/>
+                <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>80</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>80</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="3">
                   <c:v>100</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
         </c:ser>
-        <c:axId val="105140224"/>
-        <c:axId val="105472768"/>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Звед 2'!$C$3:$C$4</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>03.06.2026</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:dLbls>
+            <c:spPr/>
+            <c:txPr>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:endParaRPr lang="ru-RU"/>
+              </a:p>
+            </c:txPr>
+            <c:showSerName val="1"/>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Звед 2'!$A$5:$A$10</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>Налаштування CRM для послуг</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Джерела данних</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Канали комунікацій</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Створення акаунта</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Вхід у CRM</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Звед 2'!$C$5:$C$10</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="1">
+                  <c:v>80</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>80</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>100</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>100</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:axId val="119354112"/>
+        <c:axId val="119355648"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="105140224"/>
+        <c:axId val="119354112"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
         <c:axPos val="l"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="105472768"/>
+        <c:crossAx val="119355648"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
         <c:lblOffset val="100"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="105472768"/>
+        <c:axId val="119355648"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="100"/>
@@ -983,7 +1048,7 @@
         <c:majorGridlines/>
         <c:numFmt formatCode="General" sourceLinked="0"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="105140224"/>
+        <c:crossAx val="119354112"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1020,7 +1085,7 @@
   </c:txPr>
   <c:printSettings>
     <c:headerFooter/>
-    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageMargins b="0.75000000000000011" l="0.70000000000000007" r="0.70000000000000007" t="0.75000000000000011" header="0.30000000000000004" footer="0.30000000000000004"/>
     <c:pageSetup/>
   </c:printSettings>
 </c:chartSpace>
@@ -1132,7 +1197,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1" refreshedBy="Автор" refreshedDate="46176.89473738426" createdVersion="3" refreshedVersion="3" minRefreshableVersion="3" recordCount="29">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1" refreshedBy="Автор" refreshedDate="46177.419476736111" createdVersion="3" refreshedVersion="3" minRefreshableVersion="3" recordCount="29">
   <cacheSource type="worksheet">
     <worksheetSource ref="B2:D31" sheet="Перш"/>
   </cacheSource>
@@ -1176,9 +1241,9 @@
     <cacheField name="Дата" numFmtId="0">
       <sharedItems containsNonDate="0" containsDate="1" containsString="0" containsBlank="1" minDate="2026-06-03T00:00:00" maxDate="2026-06-06T00:00:00" count="4">
         <d v="2026-06-03T00:00:00"/>
+        <d v="2026-06-04T00:00:00"/>
         <m/>
         <d v="2026-06-05T00:00:00" u="1"/>
-        <d v="2026-06-04T00:00:00" u="1"/>
       </sharedItems>
     </cacheField>
   </cacheFields>
@@ -1209,135 +1274,135 @@
   </r>
   <r>
     <x v="4"/>
-    <m/>
+    <n v="100"/>
     <x v="1"/>
   </r>
   <r>
     <x v="5"/>
     <m/>
-    <x v="1"/>
+    <x v="2"/>
   </r>
   <r>
     <x v="6"/>
     <m/>
-    <x v="1"/>
+    <x v="2"/>
   </r>
   <r>
     <x v="7"/>
     <m/>
-    <x v="1"/>
+    <x v="2"/>
   </r>
   <r>
     <x v="8"/>
     <m/>
-    <x v="1"/>
+    <x v="2"/>
   </r>
   <r>
     <x v="9"/>
     <m/>
-    <x v="1"/>
+    <x v="2"/>
   </r>
   <r>
     <x v="10"/>
     <m/>
-    <x v="1"/>
+    <x v="2"/>
   </r>
   <r>
     <x v="11"/>
     <m/>
-    <x v="1"/>
+    <x v="2"/>
   </r>
   <r>
     <x v="12"/>
     <m/>
-    <x v="1"/>
+    <x v="2"/>
   </r>
   <r>
     <x v="13"/>
     <m/>
-    <x v="1"/>
+    <x v="2"/>
   </r>
   <r>
     <x v="14"/>
     <m/>
-    <x v="1"/>
+    <x v="2"/>
   </r>
   <r>
     <x v="15"/>
     <m/>
-    <x v="1"/>
+    <x v="2"/>
   </r>
   <r>
     <x v="16"/>
     <m/>
-    <x v="1"/>
+    <x v="2"/>
   </r>
   <r>
     <x v="17"/>
     <m/>
-    <x v="1"/>
+    <x v="2"/>
   </r>
   <r>
     <x v="18"/>
     <m/>
-    <x v="1"/>
+    <x v="2"/>
   </r>
   <r>
     <x v="19"/>
     <m/>
-    <x v="1"/>
+    <x v="2"/>
   </r>
   <r>
     <x v="20"/>
     <m/>
-    <x v="1"/>
+    <x v="2"/>
   </r>
   <r>
     <x v="21"/>
     <m/>
-    <x v="1"/>
+    <x v="2"/>
   </r>
   <r>
     <x v="22"/>
     <m/>
-    <x v="1"/>
+    <x v="2"/>
   </r>
   <r>
     <x v="23"/>
     <m/>
-    <x v="1"/>
+    <x v="2"/>
   </r>
   <r>
     <x v="24"/>
     <m/>
-    <x v="1"/>
+    <x v="2"/>
   </r>
   <r>
     <x v="25"/>
     <m/>
-    <x v="1"/>
+    <x v="2"/>
   </r>
   <r>
     <x v="26"/>
     <m/>
-    <x v="1"/>
+    <x v="2"/>
   </r>
   <r>
     <x v="27"/>
     <m/>
-    <x v="1"/>
+    <x v="2"/>
   </r>
   <r>
     <x v="28"/>
     <m/>
-    <x v="1"/>
+    <x v="2"/>
   </r>
 </pivotCacheRecords>
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="СводнаяТаблица1" cacheId="101" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Значения" updatedVersion="3" minRefreshableVersion="3" showCalcMbrs="0" useAutoFormatting="1" itemPrintTitles="1" createdVersion="3" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1">
-  <location ref="A3:C9" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="СводнаяТаблица1" cacheId="42" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Значения" updatedVersion="3" minRefreshableVersion="3" showCalcMbrs="0" useAutoFormatting="1" itemPrintTitles="1" createdVersion="3" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="4">
+  <location ref="A3:D10" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="3">
     <pivotField axis="axisRow" showAll="0">
       <items count="30">
@@ -1376,9 +1441,9 @@
     <pivotField dataField="1" showAll="0"/>
     <pivotField axis="axisCol" showAll="0">
       <items count="5">
-        <item m="1" x="2"/>
         <item m="1" x="3"/>
-        <item h="1" x="1"/>
+        <item x="1"/>
+        <item h="1" x="2"/>
         <item x="0"/>
         <item t="default"/>
       </items>
@@ -1387,7 +1452,10 @@
   <rowFields count="1">
     <field x="0"/>
   </rowFields>
-  <rowItems count="5">
+  <rowItems count="6">
+    <i>
+      <x v="23"/>
+    </i>
     <i>
       <x v="25"/>
     </i>
@@ -1407,7 +1475,10 @@
   <colFields count="1">
     <field x="2"/>
   </colFields>
-  <colItems count="2">
+  <colItems count="3">
+    <i>
+      <x v="1"/>
+    </i>
     <i>
       <x v="3"/>
     </i>
@@ -1418,7 +1489,7 @@
   <dataFields count="1">
     <dataField name="  Відсоток  виконання" fld="1" baseField="0" baseItem="0"/>
   </dataFields>
-  <chartFormats count="5">
+  <chartFormats count="11">
     <chartFormat chart="0" format="0" series="1">
       <pivotArea type="data" outline="0" fieldPosition="0">
         <references count="1">
@@ -1472,6 +1543,78 @@
           </reference>
           <reference field="2" count="1" selected="0">
             <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="1" format="6" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="1" format="7" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="3"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="2" format="8" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="2" format="9" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="3"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="3" format="8" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="3" format="9" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="3"/>
           </reference>
         </references>
       </pivotArea>
@@ -2330,7 +2473,7 @@
       <c r="C2" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="8" t="s">
         <v>30</v>
       </c>
     </row>
@@ -2382,8 +2525,12 @@
       <c r="B7" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C7" s="2"/>
-      <c r="D7" s="4"/>
+      <c r="C7" s="2">
+        <v>100</v>
+      </c>
+      <c r="D7" s="4">
+        <v>46177</v>
+      </c>
     </row>
     <row r="8" spans="2:4">
       <c r="B8" s="2" t="s">
@@ -2562,7 +2709,7 @@
       </c>
       <c r="C33" s="2">
         <f>SUM(C3:C32)</f>
-        <v>360</v>
+        <v>460</v>
       </c>
       <c r="D33" s="2"/>
     </row>
@@ -2577,17 +2724,16 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A3:C9"/>
+  <dimension ref="A3:D10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="20.7109375" customWidth="1"/>
+    <col min="1" max="1" width="29.28515625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="20.85546875" customWidth="1"/>
-    <col min="3" max="3" width="11.85546875" customWidth="1"/>
-    <col min="4" max="4" width="10.140625" customWidth="1"/>
-    <col min="5" max="6" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="6" width="11.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:4">
       <c r="A3" s="5" t="s">
         <v>34</v>
       </c>
@@ -2595,70 +2741,92 @@
         <v>35</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:4">
       <c r="A4" s="5" t="s">
         <v>32</v>
       </c>
       <c r="B4" s="3">
+        <v>46177</v>
+      </c>
+      <c r="C4" s="3">
         <v>46176</v>
       </c>
-      <c r="C4" t="s">
+      <c r="D4" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
+    <row r="5" spans="1:4">
       <c r="A5" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" s="7">
+        <v>100</v>
+      </c>
+      <c r="C5" s="7"/>
+      <c r="D5" s="7">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B5" s="7">
-        <v>80</v>
-      </c>
-      <c r="C5" s="7">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
-      <c r="A6" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B6" s="7">
-        <v>80</v>
-      </c>
+      <c r="B6" s="7"/>
       <c r="C6" s="7">
         <v>80</v>
       </c>
-    </row>
-    <row r="7" spans="1:3">
+      <c r="D6" s="7">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
       <c r="A7" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B7" s="7"/>
+      <c r="C7" s="7">
+        <v>80</v>
+      </c>
+      <c r="D7" s="7">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="B7" s="7">
-        <v>100</v>
-      </c>
-      <c r="C7" s="7">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3">
-      <c r="A8" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="B8" s="7">
-        <v>100</v>
-      </c>
+      <c r="B8" s="7"/>
       <c r="C8" s="7">
         <v>100</v>
       </c>
-    </row>
-    <row r="9" spans="1:3">
+      <c r="D8" s="7">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
       <c r="A9" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="B9" s="7"/>
+      <c r="C9" s="7">
+        <v>100</v>
+      </c>
+      <c r="D9" s="7">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="B9" s="7">
+      <c r="B10" s="7">
+        <v>100</v>
+      </c>
+      <c r="C10" s="7">
         <v>360</v>
       </c>
-      <c r="C9" s="7">
-        <v>360</v>
+      <c r="D10" s="7">
+        <v>460</v>
       </c>
     </row>
   </sheetData>
